--- a/docs/sample/expenses-template.xlsx
+++ b/docs/sample/expenses-template.xlsx
@@ -80,7 +80,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -98,10 +98,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill>
+      <patternFill patternType="none">
         <fgColor indexed="43"/>
       </patternFill>
     </fill>
@@ -126,97 +123,97 @@
   <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
       <alignment wrapText="false"/>
     </xf>
   </cellXfs>
@@ -292,7 +289,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n" s="19">
+      <c r="A4" s="19" t="n">
         <v>46023.0</v>
       </c>
       <c r="B4" t="n" s="20">
@@ -331,7 +328,7 @@
       <c r="N4" s="31">
         <f t="array" ref="N4">MEDIAN(IF($O$4:$O$500=O4,$L$4:$L$500))</f>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="10">
         <f>YEAR(A4)</f>
       </c>
       <c r="P4" s="32">
